--- a/assets/EnlightenMe.xlsx
+++ b/assets/EnlightenMe.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>score</t>
   </si>
@@ -57,6 +57,15 @@
   </si>
   <si>
     <t>signals</t>
+  </si>
+  <si>
+    <t>What am I?</t>
+  </si>
+  <si>
+    <t>I am the gps helping you navigate on your journey in life.</t>
+  </si>
+  <si>
+    <t>original nature</t>
   </si>
 </sst>
 </file>
@@ -1329,6 +1338,21 @@
       </c>
     </row>
     <row r="3" spans="1:29">
+      <c r="A3">
+        <v>200</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>

--- a/assets/EnlightenMe.xlsx
+++ b/assets/EnlightenMe.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="42">
   <si>
     <t>score</t>
   </si>
@@ -50,7 +50,7 @@
     <t>Complete this sentence.</t>
   </si>
   <si>
-    <t>Emotions are _____, not problems.</t>
+    <t>Emotions are ____, not problems.</t>
   </si>
   <si>
     <t>text</t>
@@ -66,6 +66,96 @@
   </si>
   <si>
     <t>original nature</t>
+  </si>
+  <si>
+    <t>Remove ____ to break free from the cycle of cause and effect.</t>
+  </si>
+  <si>
+    <t>ignorance</t>
+  </si>
+  <si>
+    <t>I am the first step to being at peace with your negative emotions</t>
+  </si>
+  <si>
+    <t>acceptance</t>
+  </si>
+  <si>
+    <t>Water contains _____ messages.</t>
+  </si>
+  <si>
+    <t>hidden</t>
+  </si>
+  <si>
+    <t>Emotions influence our thoughts, _____, and words.</t>
+  </si>
+  <si>
+    <t>actions</t>
+  </si>
+  <si>
+    <t>Ancient chinese scholars identified 7 emotions: joy, anger, disgust, ____, sadness, surprise, happiness.</t>
+  </si>
+  <si>
+    <t>fear</t>
+  </si>
+  <si>
+    <t>I process your emotions</t>
+  </si>
+  <si>
+    <t>amygdala</t>
+  </si>
+  <si>
+    <t>The feeling of compassion is the beginning of me.</t>
+  </si>
+  <si>
+    <t>benevolence</t>
+  </si>
+  <si>
+    <t>The feeling of shame and dislike for evil is the beginning of ______.</t>
+  </si>
+  <si>
+    <t>righteousness</t>
+  </si>
+  <si>
+    <t>The feeling of modesty and yielding is the beginning of me.</t>
+  </si>
+  <si>
+    <t>propriety</t>
+  </si>
+  <si>
+    <t>The sense of right and wrong is the beginning of _____.</t>
+  </si>
+  <si>
+    <t>wisdom</t>
+  </si>
+  <si>
+    <t>When you understand everything, you will be able to _____ all.</t>
+  </si>
+  <si>
+    <t>forgive</t>
+  </si>
+  <si>
+    <t>A ___ less resentment in my heart is a _____ more peace and harmony in the world</t>
+  </si>
+  <si>
+    <t>fraction</t>
+  </si>
+  <si>
+    <t>When people are born, their nature is fundamentally ____.</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>The _____ are not confused.</t>
+  </si>
+  <si>
+    <t>wise</t>
+  </si>
+  <si>
+    <t>The voice of conscience may be weak but is always ____.</t>
+  </si>
+  <si>
+    <t>clear</t>
   </si>
 </sst>
 </file>
@@ -701,12 +791,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1260,8 +1353,9 @@
   <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11.4454545454545" customWidth="1"/>
-    <col min="2" max="2" width="22.2727272727273" customWidth="1"/>
-    <col min="3" max="4" width="35.7363636363636" customWidth="1"/>
+    <col min="2" max="2" width="22.8909090909091" customWidth="1"/>
+    <col min="3" max="3" width="84.5090909090909" customWidth="1"/>
+    <col min="4" max="4" width="14.6363636363636" customWidth="1"/>
     <col min="5" max="5" width="30.5090909090909" customWidth="1"/>
     <col min="6" max="6" width="5.90909090909091" customWidth="1"/>
     <col min="7" max="7" width="14.6363636363636" customWidth="1"/>
@@ -1321,7 +1415,7 @@
       <c r="AC1" s="1"/>
     </row>
     <row r="2" spans="1:29">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>100</v>
       </c>
       <c r="B2" t="s">
@@ -1338,7 +1432,7 @@
       </c>
     </row>
     <row r="3" spans="1:29">
-      <c r="A3">
+      <c r="A3" s="2">
         <v>200</v>
       </c>
       <c r="B3" t="s">
@@ -1353,42 +1447,289 @@
       <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+    </row>
+    <row r="4" spans="1:29">
+      <c r="A4" s="2">
+        <v>100</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="5" spans="1:29">
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="X5" s="3"/>
+      <c r="A5" s="2">
+        <v>200</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="X5" s="4"/>
     </row>
     <row r="6" ht="16.5" spans="1:29">
-      <c r="P6" s="4"/>
+      <c r="A6" s="2">
+        <v>100</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="P6" s="5"/>
+    </row>
+    <row r="7" spans="1:29">
+      <c r="A7" s="2">
+        <v>100</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="8" spans="1:29">
-      <c r="U8" s="5"/>
+      <c r="A8" s="2">
+        <v>100</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="U8" s="6"/>
+    </row>
+    <row r="9" spans="1:29">
+      <c r="A9" s="2">
+        <v>200</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="10" spans="1:29">
-      <c r="P10" s="3"/>
-    </row>
-    <row r="20" spans="27:27">
-      <c r="AA20" s="6"/>
+      <c r="A10" s="2">
+        <v>200</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="P10" s="4"/>
+    </row>
+    <row r="11" spans="1:29">
+      <c r="A11" s="2">
+        <v>100</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29">
+      <c r="A12" s="2">
+        <v>200</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29">
+      <c r="A13" s="2">
+        <v>100</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29">
+      <c r="A14" s="2">
+        <v>100</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29">
+      <c r="A15" s="2">
+        <v>100</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29">
+      <c r="A16" s="2">
+        <v>100</v>
+      </c>
+      <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27">
+      <c r="A17" s="2">
+        <v>100</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27">
+      <c r="A18" s="2">
+        <v>100</v>
+      </c>
+      <c r="B18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27">
+      <c r="AA20" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
